--- a/outputs/Output_ImportData.xlsx
+++ b/outputs/Output_ImportData.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3917,14 +3917,10 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2 - USP net</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HNSLT_USP_STD_DEV_PREM_FLG_S03</t>
+          <t>HNSLT_USP_STD_DEV_PREM_FLG_S01</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3934,12 +3930,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>E464</t>
+          <t>E462</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>R464C5</t>
+          <t>R462C5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3965,7 +3961,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Workers' compensation</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Medical expense</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -3976,12 +3972,10 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HNSLT_USP_PREM_S03</t>
+          <t>HNSLT_USP_STD_DEV_PREM_FLG_S02</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3991,22 +3985,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>F464</t>
+          <t>E463</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>R464C6</t>
+          <t>R463C5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4014,11 +4008,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Workers' compensation</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Income protection</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -4029,12 +4027,14 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>0.05</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2 - USP net</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HNSLT_STD_PREM_HRES_SEG01</t>
+          <t>HNSLT_USP_STD_DEV_PREM_FLG_S03</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4044,22 +4044,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>E474</t>
+          <t>E464</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>R474C5</t>
+          <t>R464C5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4067,11 +4067,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Medical expense and proportional RI</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Workers' compensation</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -4082,12 +4086,10 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HNSLT_STD_PREM_HRES_SEG02</t>
+          <t>HNSLT_USP_STD_DEV_PREM_FLG_S04</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4097,22 +4099,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>E475</t>
+          <t>E465</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>R475C5</t>
+          <t>R465C5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4120,11 +4122,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Income protection and proportional RI</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Non proportional health reinsurance</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -4135,12 +4141,10 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HNSLT_STD_PREM_HRES_SEG03</t>
+          <t>HNSLT_USP_PREM_S01</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4150,12 +4154,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>E476</t>
+          <t>F462</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>R476C5</t>
+          <t>R462C6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4177,7 +4181,7 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Worker's compensation and proportional RI</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Medical expense</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -4188,12 +4192,10 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HNSLT_STD_RES_HRES_SEG01</t>
+          <t>HNSLT_USP_PREM_S02</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4203,12 +4205,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>F474</t>
+          <t>F463</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>R474C6</t>
+          <t>R463C6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4230,7 +4232,7 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Medical expense and proportional RI</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Income protection</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -4242,11 +4244,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HNSLT_STD_RES_HRES_SEG02</t>
+          <t>HNSLT_USP_PREM_S03</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4256,12 +4258,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>F475</t>
+          <t>F464</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>R475C6</t>
+          <t>R464C6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4283,7 +4285,7 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Income protection and proportional RI</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Workers' compensation</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
@@ -4294,12 +4296,10 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HNSLT_STD_RES_HRES_SEG03</t>
+          <t>HNSLT_USP_PREM_S04</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>F476</t>
+          <t>F465</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>R476C6</t>
+          <t>R465C6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4336,7 +4336,7 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Worker's compensation and proportional RI</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Non proportional health reinsurance</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -4344,15 +4344,13 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Health NSLT Lapse</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>6879.6</v>
-      </c>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HNSLT_LAPSE_A_BC</t>
+          <t>HNSLT_USP_RES_S01</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4362,12 +4360,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>E132</t>
+          <t>G462</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>R132C5</t>
+          <t>R462C7</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4382,34 +4380,28 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Health non SLT lapse risk - Assets - Initial value</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Article 150 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Health - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Medical expense</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Health NSLT Lapse</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>6779.6</v>
-      </c>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HNSLT_LAPSE_A_SH</t>
+          <t>HNSLT_USP_RES_S02</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4419,12 +4411,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>E133</t>
+          <t>G463</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>R133C5</t>
+          <t>R463C7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4439,34 +4431,28 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Health non SLT lapse risk - Assets - Value after a mass shock (net)</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Article 150 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Health - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Income protection</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Health NSLT Lapse</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>-6779.6</v>
-      </c>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HNSLT_LAPSE_L_BC</t>
+          <t>HNSLT_USP_RES_S03</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4476,12 +4462,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>F132</t>
+          <t>G464</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>R132C6</t>
+          <t>R464C7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4496,34 +4482,28 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Health non SLT lapse risk - Liabilities - Initial value</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Article 150 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Health - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Workers' compensation</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Health NSLT Lapse</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>-4067.76</v>
-      </c>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HNSLT_LAPSE_L_SH</t>
+          <t>HNSLT_USP_RES_S04</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4533,12 +4513,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>F133</t>
+          <t>G465</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>R133C6</t>
+          <t>R465C7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4553,36 +4533,28 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Health non SLT lapse risk - Liabilities - Value after a mass shock (net)</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Article 150 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Health - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Non proportional health reinsurance</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NL_CAP_SIMPL</t>
+          <t>HNSLT_USP_NP_FAC_ADJ_S01</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4592,22 +4564,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>E183</t>
+          <t>H462</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>R183C5</t>
+          <t>R462C8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4615,19 +4587,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Captives simplifications - premium and reserve risk (y/n)</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Medical expense</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -4635,17 +4599,13 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG01</t>
+          <t>HNSLT_USP_NP_FAC_ADJ_S02</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4655,22 +4615,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>E187</t>
+          <t>H463</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>R187C5</t>
+          <t>R463C8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4678,19 +4638,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Motor vehicle liability insurance and proportional RI</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Income protection</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -4698,17 +4650,13 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG02</t>
+          <t>HNSLT_USP_NP_FAC_ADJ_S03</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4718,22 +4666,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>E188</t>
+          <t>H464</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>R188C5</t>
+          <t>R464C8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4741,19 +4689,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Other motor insurance and proportional RI</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Workers' compensation</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -4761,17 +4701,13 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG03</t>
+          <t>HNSLT_USP_NP_FAC_ADJ_S04</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4781,22 +4717,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>E189</t>
+          <t>H465</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>R189C5</t>
+          <t>R465C8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4804,19 +4740,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Marine, aviation and transport insurance and proportional RI</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Non proportional health reinsurance</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -4824,17 +4752,15 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.05</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG04</t>
+          <t>HNSLT_STD_PREM_HRES_SEG01</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4844,22 +4770,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>E190</t>
+          <t>E474</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>R190C5</t>
+          <t>R474C5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4867,19 +4793,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Fire and other damage to property insurance and proportional RI</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Medical expense and proportional RI</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -4887,17 +4805,15 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.05</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG05</t>
+          <t>HNSLT_STD_PREM_HRES_SEG02</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4907,22 +4823,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>E191</t>
+          <t>E475</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>R191C5</t>
+          <t>R475C5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4930,19 +4846,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - General liability insurance and proportional RI</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Income protection and proportional RI</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -4950,17 +4858,15 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.05</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG06</t>
+          <t>HNSLT_STD_PREM_HRES_SEG03</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4970,22 +4876,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>E192</t>
+          <t>E476</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>R192C5</t>
+          <t>R476C5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4993,19 +4899,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Credit and suretyship insurance and proportional RI</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Worker's compensation and proportional RI</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -5013,17 +4911,15 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.05</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG07</t>
+          <t>HNSLT_STD_RES_HRES_SEG01</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5033,22 +4929,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>E193</t>
+          <t>F474</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>R193C5</t>
+          <t>R474C6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5056,19 +4952,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Legal expenses insurance and proportional RI</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Medical expense and proportional RI</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -5076,17 +4964,15 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.05</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG08</t>
+          <t>HNSLT_STD_RES_HRES_SEG02</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5096,22 +4982,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>E194</t>
+          <t>F475</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>R194C5</t>
+          <t>R475C6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5119,19 +5005,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Assistance and its proportional RI</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Income protection and proportional RI</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -5139,17 +5017,15 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.05</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG09</t>
+          <t>HNSLT_STD_RES_HRES_SEG03</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5159,22 +5035,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>E195</t>
+          <t>F476</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>R195C5</t>
+          <t>R476C6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5182,19 +5058,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Misceallaneous financial loss insurance and proportional RI</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Worker's compensation and proportional RI</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -5202,17 +5070,15 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Health NSLT Lapse</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>6879.6</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG10</t>
+          <t>HNSLT_LAPSE_A_BC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5222,60 +5088,54 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>E196</t>
+          <t>E132</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>R196C5</t>
+          <t>R132C5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional casualty RI</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr"/>
+          <t>Health non SLT lapse risk - Assets - Initial value</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Article 150 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Health NSLT Lapse</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>6779.6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG11</t>
+          <t>HNSLT_LAPSE_A_SH</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5285,60 +5145,54 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>E197</t>
+          <t>E133</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>R197C5</t>
+          <t>R133C5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional marine, aviation and transport RI </t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr"/>
+          <t>Health non SLT lapse risk - Assets - Value after a mass shock (net)</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Article 150 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Health NSLT Lapse</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>-6779.6</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG12</t>
+          <t>HNSLT_LAPSE_L_BC</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5348,60 +5202,54 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>E198</t>
+          <t>F132</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>R198C5</t>
+          <t>R132C6</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional property RI</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
+          <t>Health non SLT lapse risk - Liabilities - Initial value</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Article 150 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2 - USP net</t>
-        </is>
+          <t>Health NSLT Lapse</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>-4067.76</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S03</t>
+          <t>HNSLT_LAPSE_L_SH</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5411,41 +5259,41 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>E491</t>
+          <t>F133</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>R491C5</t>
+          <t>R133C6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Marine, aviation, transport (MAT)</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
+          <t>Health non SLT lapse risk - Liabilities - Value after a mass shock (net)</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Article 150 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5453,12 +5301,14 @@
           <t>Non-Life Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>0.08</v>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S03</t>
+          <t>NL_CAP_SIMPL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5468,22 +5318,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>F491</t>
+          <t>E183</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>R491C6</t>
+          <t>R183C5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5491,11 +5341,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Marine, aviation, transport (MAT)</t>
+          <t>Non-life underwriting risk input - Captives simplifications - premium and reserve risk (y/n)</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -5503,15 +5361,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>6789.6</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NL_LAPSE_A_BC</t>
+          <t>NL_ART_116_4_FLG_SEG01</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5521,54 +5381,60 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>E215</t>
+          <t>E187</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>R215C5</t>
+          <t>R187C5</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Non-life lapse risk - Assets - Initial value</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Article 118 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Motor vehicle liability insurance and proportional RI</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>6779.6</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NL_LAPSE_A_SH</t>
+          <t>NL_ART_116_4_FLG_SEG02</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5578,54 +5444,60 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>E216</t>
+          <t>E188</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>R216C5</t>
+          <t>R188C5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Non-life lapse risk - Assets - Value after a mass shock (net)</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Article 118 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Other motor insurance and proportional RI</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>-6779.6</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NL_LAPSE_L_BC</t>
+          <t>NL_ART_116_4_FLG_SEG03</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5635,54 +5507,60 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>F215</t>
+          <t>E189</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>R215C6</t>
+          <t>R189C5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Non-life lapse risk - Liabilities - Initial value</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Article 118 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Marine, aviation and transport insurance and proportional RI</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>-4067.76</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NL_LAPSE_L_SH</t>
+          <t>NL_ART_116_4_FLG_SEG04</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5692,54 +5570,60 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>F216</t>
+          <t>E190</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>R216C6</t>
+          <t>R190C5</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Non-life lapse risk - Liabilities - Value after a mass shock (net)</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Article 118 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Fire and other damage to property insurance and proportional RI</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>300</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NL_WS_OTH_REG_RM</t>
+          <t>NL_ART_116_4_FLG_SEG05</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5749,34 +5633,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>E250</t>
+          <t>E191</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>R250C5</t>
+          <t>R191C5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Windstorm - Other regions - Risk Mitigation</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - General liability insurance and proportional RI</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -5784,15 +5676,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>300</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NL_WS_OTH_REG_RM_WONB</t>
+          <t>NL_ART_116_4_FLG_SEG06</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5802,34 +5696,42 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>F250</t>
+          <t>E192</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>R250C6</t>
+          <t>R192C5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Windstorm - Other regions - Risk Mitigation - Without new business</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Credit and suretyship insurance and proportional RI</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -5837,15 +5739,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>100</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NL_WS_OTH_REG_REINS_PREM</t>
+          <t>NL_ART_116_4_FLG_SEG07</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5855,34 +5759,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>E251</t>
+          <t>E193</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>R251C5</t>
+          <t>R193C5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Windstorm - Other regions - Estimated Reinstatement Premiums</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Legal expenses insurance and proportional RI</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -5890,15 +5802,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>300</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NL_EQ_OTH_REG_RM</t>
+          <t>NL_ART_116_4_FLG_SEG08</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5908,34 +5822,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>E252</t>
+          <t>E194</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>R252C5</t>
+          <t>R194C5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Earthquake - Other regions - Risk Mitigation</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Assistance and its proportional RI</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -5943,15 +5865,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>300</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NL_EQ_OTH_REG_RM_WONB</t>
+          <t>NL_ART_116_4_FLG_SEG09</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5961,34 +5885,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>F252</t>
+          <t>E195</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>R252C6</t>
+          <t>R195C5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Earthquake - Other regions - Estimated Reinstatement Premiums</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Misceallaneous financial loss insurance and proportional RI</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -5996,15 +5928,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>100</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NL_EQ_OTH_REG_REINS_PREM</t>
+          <t>NL_ART_116_4_FLG_SEG10</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6014,34 +5948,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>E253</t>
+          <t>E196</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>R253C5</t>
+          <t>R196C5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Earthquake - Other regions - Risk Mitigation - Without new business</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional casualty RI</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -6049,15 +5991,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>300</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NL_FL_OTH_REG_RM</t>
+          <t>NL_ART_116_4_FLG_SEG11</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6067,34 +6011,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>E254</t>
+          <t>E197</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>R254C5</t>
+          <t>R197C5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Flood - Other regions - Risk Mitigation</t>
+          <t xml:space="preserve">Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional marine, aviation and transport RI </t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -6102,15 +6054,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>300</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NL_FL_OTH_REG_RM_WONB</t>
+          <t>NL_ART_116_4_FLG_SEG12</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6120,34 +6074,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>F254</t>
+          <t>E198</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>R254C6</t>
+          <t>R198C5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Flood - Other regions - Estimated Reinstatement Premiums</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional property RI</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -6155,15 +6117,13 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>100</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NL_FL_OTH_REG_REINS_PREM</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S01</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6173,34 +6133,38 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>E255</t>
+          <t>E489</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>R255C5</t>
+          <t>R489C5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Flood - Other regions - Risk Mitigation - Without new business</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Motor vehicle liability</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -6208,15 +6172,13 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>300</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NL_HA_OTH_REG_RM</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S02</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6226,34 +6188,38 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>E256</t>
+          <t>E490</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>R256C5</t>
+          <t>R490C5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Hail - Other regions - Risk Mitigation</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Motor, other classes</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -6261,15 +6227,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>300</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2 - USP net</t>
+        </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NL_HA_OTH_REG_RM_WONB</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S03</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6279,34 +6247,38 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>F256</t>
+          <t>E491</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>R256C6</t>
+          <t>R491C5</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Hail - Other regions - Estimated Reinstatement Premiums</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Marine, aviation, transport (MAT)</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -6314,15 +6286,13 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>100</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NL_HA_OTH_REG_REINS_PREM</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S04</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6332,34 +6302,38 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>E257</t>
+          <t>E492</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>R257C5</t>
+          <t>R492C5</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Hail - Other regions - Risk Mitigation - Without new business</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Fire and other property damage</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -6367,15 +6341,13 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>2000</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NL_NPPRI_PREM_EARN_G_NY_EB</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S05</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6385,34 +6357,38 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>E272</t>
+          <t>E493</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>R272C5</t>
+          <t>R493C5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Gross premium to be earned - Existing business</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Third-party liability</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -6420,15 +6396,13 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NL_NPPRI_PREM_EARN_G_NY_NB</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S06</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6438,34 +6412,38 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>F272</t>
+          <t>E494</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>R272C6</t>
+          <t>R494C5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Gross premium to be earned - New business</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Credit and suretyship</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -6473,15 +6451,13 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>300</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NL_NPPRI_RM</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S07</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6491,34 +6467,38 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>E278</t>
+          <t>E495</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>R278C5</t>
+          <t>R495C5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Risk Mitigation</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Legal expenses</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -6526,15 +6506,13 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>300</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NL_NPPRI_RM_WONB</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S08</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6544,34 +6522,38 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>F278</t>
+          <t>E496</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>R278C6</t>
+          <t>R496C5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Risk Mitigation - Without new business</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Assistance</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -6579,15 +6561,13 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>100</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NL_NPPRI_REINS_PREM</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6597,34 +6577,38 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>E279</t>
+          <t>E497</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>R279C5</t>
+          <t>R497C5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Estimated Reinstatement Premiums</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Miscellaneous</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -6632,15 +6616,13 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP1</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6650,34 +6632,38 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>E297</t>
+          <t>E498</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>R297C5</t>
+          <t>R498C5</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Non-proportional reinsurance - casualty</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -6685,15 +6671,13 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP2</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6703,34 +6687,38 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>E298</t>
+          <t>E499</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>R298C5</t>
+          <t>R499C5</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Non-proportional reinsurance - MAT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -6738,15 +6726,13 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP3</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6756,34 +6742,38 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>E299</t>
+          <t>E500</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>R299C5</t>
+          <t>R500C5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Non-proportional reinsurance - property</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -6791,15 +6781,13 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP4</t>
+          <t>NL_USP_PREM_S01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6809,12 +6797,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>E300</t>
+          <t>F489</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>R300C5</t>
+          <t>R489C6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6829,14 +6817,14 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional casualty RI other than General Liability RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Motor vehicle liability</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -6844,15 +6832,13 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP5</t>
+          <t>NL_USP_PREM_S02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6862,12 +6848,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>E301</t>
+          <t>F490</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>R301C5</t>
+          <t>R490C6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6882,14 +6868,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional Credit &amp; Suretyship RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Motor, other classes</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -6897,15 +6883,15 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
+          <t>Non-Life Prem. &amp; Res.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_GROUP1</t>
+          <t>NL_USP_PREM_S03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6915,12 +6901,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>G297</t>
+          <t>F491</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>R297C7</t>
+          <t>R491C6</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6935,14 +6921,14 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Marine, aviation, transport (MAT)</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -6950,15 +6936,13 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_GROUP2</t>
+          <t>NL_USP_PREM_S04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6968,12 +6952,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>G298</t>
+          <t>F492</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>R298C7</t>
+          <t>R492C6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6988,14 +6972,14 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Fire and other property damage</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -7003,15 +6987,13 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_GROUP3</t>
+          <t>NL_USP_PREM_S05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7021,12 +7003,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>G299</t>
+          <t>F493</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>R299C7</t>
+          <t>R493C6</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7041,14 +7023,14 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Third-party liability</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -7056,15 +7038,13 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_GROUP4</t>
+          <t>NL_USP_PREM_S06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7074,12 +7054,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>G300</t>
+          <t>F494</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>R300C7</t>
+          <t>R494C6</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7094,14 +7074,14 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional casualty RI other than General Liability RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Credit and suretyship</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -7109,15 +7089,13 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_GROUP5</t>
+          <t>NL_USP_PREM_S07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7127,12 +7105,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>G301</t>
+          <t>F495</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>R301C7</t>
+          <t>R495C6</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7147,14 +7125,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional Credit &amp; Suretyship RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Legal expenses</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -7162,15 +7140,13 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP1</t>
+          <t>NL_USP_PREM_S08</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7180,12 +7156,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>H297</t>
+          <t>F496</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>R297C8</t>
+          <t>R496C6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7200,14 +7176,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Assistance</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -7215,15 +7191,13 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP2</t>
+          <t>NL_USP_PREM_S09</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7233,12 +7207,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>H298</t>
+          <t>F497</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>R298C8</t>
+          <t>R497C6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7253,14 +7227,14 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Miscellaneous</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -7268,15 +7242,13 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP3</t>
+          <t>NL_USP_PREM_S10</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7286,12 +7258,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>H299</t>
+          <t>F498</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>R299C8</t>
+          <t>R498C6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7306,14 +7278,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Non-proportional reinsurance - casualty</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -7321,15 +7293,13 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP4</t>
+          <t>NL_USP_PREM_S11</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7339,12 +7309,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>H300</t>
+          <t>F499</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>R300C8</t>
+          <t>R499C6</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7359,14 +7329,14 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional casualty RI other than General Liability RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Non-proportional reinsurance - MAT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -7374,15 +7344,13 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP5</t>
+          <t>NL_USP_PREM_S12</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7392,12 +7360,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>H301</t>
+          <t>F500</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>R301C8</t>
+          <t>R500C6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7412,14 +7380,14 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional Credit &amp; Suretyship RI</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Non-proportional reinsurance - property</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -7427,17 +7395,13 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Risk Margin</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Method 3</t>
-        </is>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>RM_METHOD</t>
+          <t>NL_USP_RES_S01</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7447,17 +7411,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>G489</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>R37C5</t>
+          <t>R489C7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7470,15 +7434,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Risk Margin Method</t>
-        </is>
-      </c>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Risk margin - Method chosen for risk margin calculations</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Motor vehicle liability</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -7486,17 +7446,13 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Risk Margin</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>RM_ART_116_147_4_FLG</t>
+          <t>NL_USP_RES_S02</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7506,22 +7462,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>E39</t>
+          <t>G490</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>R39C5</t>
+          <t>R490C7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7529,19 +7485,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Risk margin - Article 116 (4) and Article 147 (4) applicable?</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Motor, other classes</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -7549,17 +7497,13 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Risk Margin - Method 2</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>net SCR</t>
-        </is>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>RM_PROJECTION</t>
+          <t>NL_USP_RES_S03</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7569,17 +7513,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>E38</t>
+          <t>G491</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>R38C5</t>
+          <t>R491C7</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7592,19 +7536,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>Projection method 2</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>gross SCR</t>
-        </is>
-      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Risk margin - Method 2 - Projection of gross or net SCR</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Marine, aviation, transport (MAT)</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -7612,17 +7548,13 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Risk Margin - Split</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>RM_TC_SPLIT_FLG</t>
+          <t>NL_USP_RES_S04</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7632,22 +7564,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>E43</t>
+          <t>G492</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>R43C5</t>
+          <t>R492C7</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7655,19 +7587,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Risk margin - Allocation - Split of Risk Margin by currency necessary?</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Fire and other property damage</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -7675,17 +7599,13 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Risk Margin - Split</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>RM_TC_SPLIT_ALLOC_FLG</t>
+          <t>NL_USP_RES_S05</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7695,22 +7615,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>E44</t>
+          <t>G493</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>R44C5</t>
+          <t>R493C7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7718,19 +7638,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Risk margin - Split by currency - Flag for allocation factors</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Third-party liability</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -7738,15 +7650,13 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>0.08</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LIFE_REV_SHOCK_USP</t>
+          <t>NL_USP_RES_S06</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7756,12 +7666,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>E439</t>
+          <t>G494</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>R439C5</t>
+          <t>R494C7</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7783,7 +7693,7 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Life underwriting risk - Revision Risk - Revision shock used - USP </t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Credit and suretyship</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -7791,15 +7701,13 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Health SLT</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0.04</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>HSLT_REV_SHOCK_USP</t>
+          <t>NL_USP_RES_S07</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7809,12 +7717,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>E447</t>
+          <t>G495</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>R447C5</t>
+          <t>R495C7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7836,7 +7744,7 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLT health underwriting risk - Revision Risk - Revision shock used - USP </t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Legal expenses</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -7844,15 +7752,13 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>548</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NSCR_REMAINING_PART</t>
+          <t>NL_USP_RES_S08</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7862,12 +7768,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>F545</t>
+          <t>G496</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>R545C6</t>
+          <t>R496C7</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -7882,34 +7788,28 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Total amount of Notional Solvency Capital Requirements for remaining part</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Assistance</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>450</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NSCR_RFF</t>
+          <t>NL_USP_RES_S09</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7919,12 +7819,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>F546</t>
+          <t>G497</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>R546C6</t>
+          <t>R497C7</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -7939,34 +7839,28 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Total amount of Notional Solvency Capital Requirements for ring fenced funds</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Miscellaneous</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>666</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NSCR_MAP</t>
+          <t>NL_USP_RES_S10</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7976,12 +7870,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>F547</t>
+          <t>G498</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>R547C6</t>
+          <t>R498C7</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -7996,34 +7890,28 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Total amount of Notional Solvency Capital Requirement for matching adjustment portfolios</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Non-proportional reinsurance - casualty</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>-981</v>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DIV_EFFECT_RFF_304</t>
+          <t>NL_USP_RES_S11</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8033,12 +7921,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>F548</t>
+          <t>G499</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>R548C6</t>
+          <t>R499C7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8053,36 +7941,28 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Diversification effects due to RFF nSCR aggregation for article 304</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>Article 216 (2.) [2015/35/EU]; Article 304 [2009/138/EC]</t>
-        </is>
-      </c>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Non-proportional reinsurance - MAT</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>4 = No adjustment (Default Value)</t>
-        </is>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ADJ_RFF_MAP_METH</t>
+          <t>NL_USP_RES_S12</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8092,22 +7972,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>F549</t>
+          <t>G500</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>R549C6</t>
+          <t>R500C7</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8115,41 +7995,25 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>List RFF/MAP Method</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>4 = No adjustment (Default Value)</t>
-        </is>
-      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Method used to calculate the adjustment due to RFF/MAP nSCR aggregation </t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>Cell on S.25.01.01 QRT</t>
-        </is>
-      </c>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Non-proportional reinsurance - property</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HNSLT_LAPSE_SIMPL</t>
+          <t>NL_USP_NP_FAC_ADJ_S01</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8159,22 +8023,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>E140</t>
+          <t>H489</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>R140C5</t>
+          <t>R489C8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8182,19 +8046,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Simplification NSLT</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Simplification Health</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Motor vehicle liability</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -8202,17 +8058,13 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NL_LAPSE_SIMPL</t>
+          <t>NL_USP_NP_FAC_ADJ_S02</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8222,22 +8074,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>E221</t>
+          <t>H490</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>R221C5</t>
+          <t>R490C8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8245,19 +8097,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>Simplification NSLT NL</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Simplification Non Life</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Motor, other classes</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -8268,14 +8112,10 @@
           <t>Non-Life Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NL_WS_SIMPL</t>
+          <t>NL_USP_NP_FAC_ADJ_S03</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8285,22 +8125,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>E237</t>
+          <t>H491</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>R237C5</t>
+          <t>R491C8</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8308,81 +8148,3918 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>Simplification NC</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Marine, aviation, transport (MAT)</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NL_USP_NP_FAC_ADJ_S04</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>H492</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>R492C8</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Fire and other property damage</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>NL_USP_NP_FAC_ADJ_S05</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>H493</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>R493C8</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Third-party liability</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>NL_USP_NP_FAC_ADJ_S06</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>H494</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>R494C8</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Credit and suretyship</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NL_USP_NP_FAC_ADJ_S07</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>H495</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>R495C8</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Legal expenses</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NL_USP_NP_FAC_ADJ_S08</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>H496</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>R496C8</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Assistance</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>NL_USP_NP_FAC_ADJ_S09</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>H497</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>R497C8</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Miscellaneous</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>NL_USP_NP_FAC_ADJ_S10</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>H498</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>R498C8</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Non-proportional reinsurance - casualty</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NL_USP_NP_FAC_ADJ_S11</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>H499</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>R499C8</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Non-proportional reinsurance - MAT</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>NL_USP_NP_FAC_ADJ_S12</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>H500</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>R500C8</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Non-proportional reinsurance - property</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>6789.6</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>NL_LAPSE_A_BC</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>E215</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>R215C5</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Non-life lapse risk - Assets - Initial value</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Article 118 [2015/35/EU]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>6779.6</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>NL_LAPSE_A_SH</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>E216</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>R216C5</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Non-life lapse risk - Assets - Value after a mass shock (net)</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Article 118 [2015/35/EU]</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>-6779.6</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>NL_LAPSE_L_BC</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>F215</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>R215C6</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Non-life lapse risk - Liabilities - Initial value</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Article 118 [2015/35/EU]</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>-4067.76</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>NL_LAPSE_L_SH</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>F216</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>R216C6</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Non-life lapse risk - Liabilities - Value after a mass shock (net)</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Article 118 [2015/35/EU]</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>300</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>NL_WS_OTH_REG_RM</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>E250</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>R250C5</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Windstorm - Other regions - Risk Mitigation</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>300</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NL_WS_OTH_REG_RM_WONB</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>F250</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>R250C6</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Windstorm - Other regions - Risk Mitigation - Without new business</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>100</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>NL_WS_OTH_REG_REINS_PREM</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>E251</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>R251C5</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Windstorm - Other regions - Estimated Reinstatement Premiums</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>NL_WS_OTH_REG_REINS_PREM_WONB</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>F251</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>R251C6</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Windstorm - Other regions - Estimated Reinstatement Premiums - Without new business</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>300</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>NL_EQ_OTH_REG_RM</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>E252</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>R252C5</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Earthquake - Other regions - Risk Mitigation</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>300</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>NL_EQ_OTH_REG_RM_WONB</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>F252</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>R252C6</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Earthquake - Other regions - Estimated Reinstatement Premiums</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>100</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>NL_EQ_OTH_REG_REINS_PREM</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>E253</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>R253C5</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Earthquake - Other regions - Risk Mitigation - Without new business</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>NL_EQ_OTH_REG_REINS_PREM_WONB</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>F253</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>R253C6</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Earthquake - Other regions - Estimated Reinstatement Premiums - Without new business</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>300</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>NL_FL_OTH_REG_RM</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>E254</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>R254C5</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Flood - Other regions - Risk Mitigation</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>300</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>NL_FL_OTH_REG_RM_WONB</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>F254</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>R254C6</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Flood - Other regions - Estimated Reinstatement Premiums</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>100</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>NL_FL_OTH_REG_REINS_PREM</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>E255</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>R255C5</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Flood - Other regions - Risk Mitigation - Without new business</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>NL_FL_OTH_REG_REINS_PREM_WONB</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>F255</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>R255C6</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Flood - Other regions - Estimated Reinstatement Premiums - Without new business</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>300</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>NL_HA_OTH_REG_RM</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>E256</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>R256C5</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Hail - Other regions - Risk Mitigation</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>300</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>NL_HA_OTH_REG_RM_WONB</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>F256</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>R256C6</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Hail - Other regions - Estimated Reinstatement Premiums</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>100</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>NL_HA_OTH_REG_REINS_PREM</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>E257</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>R257C5</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Hail - Other regions - Risk Mitigation - Without new business</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>NL_HA_OTH_REG_REINS_PREM_WONB</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>F257</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>R257C6</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Hail - Other regions - Estimated Reinstatement Premiums - Without new business</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>NL_NPPRI_PREM_EARN_G_NY_EB</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>E272</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>R272C5</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Gross premium to be earned - Existing business</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NL_NPPRI_PREM_EARN_G_NY_NB</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>F272</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>R272C6</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Gross premium to be earned - New business</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>300</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>NL_NPPRI_RM</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>E278</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>R278C5</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Risk Mitigation</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>300</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NL_NPPRI_RM_WONB</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>F278</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>R278C6</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Risk Mitigation - Without new business</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>100</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>NL_NPPRI_REINS_PREM</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>E279</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>R279C5</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Estimated Reinstatement Premiums</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP1</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>E297</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>R297C5</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP2</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>E298</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>R298C5</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>E299</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>R299C5</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP4</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>E300</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>R300C5</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional casualty RI other than General Liability RI</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP5</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>E301</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>R301C5</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional Credit &amp; Suretyship RI</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP1</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>F297</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>R297C6</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP2</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>F298</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>R298C6</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>F299</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>R299C6</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP4</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>R300C6</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Non-proportional casualty RI other than General Liability RI</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP5</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>F301</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>R301C6</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Non-proportional Credit &amp; Suretyship RI</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>0</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_GROUP1</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>G297</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>R297C7</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_GROUP2</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>G298</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>R298C7</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_GROUP3</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>G299</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>R299C7</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_GROUP4</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>G300</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>R300C7</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional casualty RI other than General Liability RI</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_GROUP5</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>G301</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>R301C7</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional Credit &amp; Suretyship RI</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_WONB_GROUP1</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>H297</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>R297C8</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_WONB_GROUP2</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>H298</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>R298C8</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_WONB_GROUP3</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>H299</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>R299C8</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>0</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_WONB_GROUP4</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>H300</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>R300C8</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional casualty RI other than General Liability RI</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>NL_OTHCAT_RM_WONB_GROUP5</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>H301</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>R301C8</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional Credit &amp; Suretyship RI</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Risk Margin</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Method 3</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>RM_METHOD</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>E37</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>R37C5</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Risk Margin Method</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Risk margin - Method chosen for risk margin calculations</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Risk Margin</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>RM_ART_116_147_4_FLG</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>E39</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>R39C5</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Risk margin - Article 116 (4) and Article 147 (4) applicable?</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Risk Margin - Method 2</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>net SCR</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>RM_PROJECTION</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>R38C5</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Projection method 2</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>gross SCR</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Risk margin - Method 2 - Projection of gross or net SCR</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Risk Margin - Split</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>RM_TC_SPLIT_FLG</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>E43</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>R43C5</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Risk margin - Allocation - Split of Risk Margin by currency necessary?</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Risk Margin - Split</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>RM_TC_SPLIT_ALLOC_FLG</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>E44</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>R44C5</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Risk margin - Split by currency - Flag for allocation factors</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>LIFE_REV_SHOCK_USP</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>E439</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>R439C5</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Life underwriting risk - Revision Risk - Revision shock used - USP </t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Health SLT</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>HSLT_REV_SHOCK_USP</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>E447</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>R447C5</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLT health underwriting risk - Revision Risk - Revision shock used - USP </t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>548</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>NSCR_REMAINING_PART</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>F545</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>R545C6</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Total amount of Notional Solvency Capital Requirements for remaining part</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>450</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>NSCR_RFF</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>F546</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>R546C6</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Total amount of Notional Solvency Capital Requirements for ring fenced funds</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>666</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>NSCR_MAP</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>F547</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>R547C6</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Total amount of Notional Solvency Capital Requirement for matching adjustment portfolios</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>-981</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>DIV_EFFECT_RFF_304</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>F548</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>R548C6</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Diversification effects due to RFF nSCR aggregation for article 304</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Article 216 (2.) [2015/35/EU]; Article 304 [2009/138/EC]</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>4 = No adjustment (Default Value)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ADJ_RFF_MAP_METH</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>F549</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>R549C6</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>List RFF/MAP Method</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>4 = No adjustment (Default Value)</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method used to calculate the adjustment due to RFF/MAP nSCR aggregation </t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Cell on S.25.01.01 QRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>HNSLT_LAPSE_SIMPL</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>E140</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>R140C5</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Simplification NSLT</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Simplification Health</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>NL_LAPSE_SIMPL</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>E221</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>R221C5</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Simplification NSLT NL</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Simplification Non Life</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>NL_WS_SIMPL</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>E237</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>R237C5</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Simplification NC</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SCR</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SCR_PRELIMINARY_VTP</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>E47</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>R47C5</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Preliminary SCR</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SCR</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SCR_PRELIMINARY_TTP</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>E48</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>R48C5</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Preliminary SCR</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
           <t>Participant information</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Standard Formula</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>INFO_TYPE_OF_MODEL</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Basic input</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
         <is>
           <t>E18</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>R18C5</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H213" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
         <is>
           <t>Type of Model</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="K213" t="inlineStr">
         <is>
           <t>Standard Formula</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t>Internal Model</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Output_ImportData.xlsx
+++ b/outputs/Output_ImportData.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M213"/>
+  <dimension ref="A1:M142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3917,10 +3917,14 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2 - USP net</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HNSLT_USP_STD_DEV_PREM_FLG_S01</t>
+          <t>HNSLT_USP_STD_DEV_PREM_FLG_S03</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3930,12 +3934,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>E462</t>
+          <t>E464</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>R462C5</t>
+          <t>R464C5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3961,7 +3965,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Medical expense</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Workers' compensation</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -3972,10 +3976,12 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>0.06</v>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HNSLT_USP_STD_DEV_PREM_FLG_S02</t>
+          <t>HNSLT_USP_PREM_S03</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3985,22 +3991,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>E463</t>
+          <t>F464</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>R463C5</t>
+          <t>R464C6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4008,15 +4014,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Income protection</t>
+          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Workers' compensation</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -4027,14 +4029,12 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2 - USP net</t>
-        </is>
+      <c r="B66" t="n">
+        <v>0.05</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HNSLT_USP_STD_DEV_PREM_FLG_S03</t>
+          <t>HNSLT_STD_PREM_HRES_SEG01</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4044,22 +4044,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>E464</t>
+          <t>E474</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>R464C5</t>
+          <t>R474C5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4067,15 +4067,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Workers' compensation</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Medical expense and proportional RI</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -4086,10 +4082,12 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0.05</v>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HNSLT_USP_STD_DEV_PREM_FLG_S04</t>
+          <t>HNSLT_STD_PREM_HRES_SEG02</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4099,22 +4097,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>E465</t>
+          <t>E475</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>R465C5</t>
+          <t>R475C5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4122,15 +4120,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Non proportional health reinsurance</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Income protection and proportional RI</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -4141,10 +4135,12 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0.05</v>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HNSLT_USP_PREM_S01</t>
+          <t>HNSLT_STD_PREM_HRES_SEG03</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4154,12 +4150,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>F462</t>
+          <t>E476</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>R462C6</t>
+          <t>R476C5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4181,7 +4177,7 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Medical expense</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Worker's compensation and proportional RI</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -4192,10 +4188,12 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="n">
+        <v>0.05</v>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HNSLT_USP_PREM_S02</t>
+          <t>HNSLT_STD_RES_HRES_SEG01</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4205,12 +4203,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>F463</t>
+          <t>F474</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>R463C6</t>
+          <t>R474C6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4232,7 +4230,7 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Income protection</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Medical expense and proportional RI</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -4244,11 +4242,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HNSLT_USP_PREM_S03</t>
+          <t>HNSLT_STD_RES_HRES_SEG02</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4258,12 +4256,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>F464</t>
+          <t>F475</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>R464C6</t>
+          <t>R475C6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4285,7 +4283,7 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Workers' compensation</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Income protection and proportional RI</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
@@ -4296,10 +4294,12 @@
           <t>Health NSLT Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="n">
+        <v>0.05</v>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HNSLT_USP_PREM_S04</t>
+          <t>HNSLT_STD_RES_HRES_SEG03</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>F465</t>
+          <t>F476</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>R465C6</t>
+          <t>R476C6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4336,7 +4336,7 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Premium risk Segment: Non proportional health reinsurance</t>
+          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Worker's compensation and proportional RI</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -4344,13 +4344,15 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>Health NSLT Lapse</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>6879.6</v>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HNSLT_USP_RES_S01</t>
+          <t>HNSLT_LAPSE_A_BC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4360,12 +4362,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>G462</t>
+          <t>E132</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>R462C7</t>
+          <t>R132C5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4380,28 +4382,34 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Medical expense</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>Health non SLT lapse risk - Assets - Initial value</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Article 150 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>Health NSLT Lapse</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>6779.6</v>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HNSLT_USP_RES_S02</t>
+          <t>HNSLT_LAPSE_A_SH</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4411,12 +4419,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>G463</t>
+          <t>E133</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>R463C7</t>
+          <t>R133C5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4431,28 +4439,34 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Income protection</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>Health non SLT lapse risk - Assets - Value after a mass shock (net)</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Article 150 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>Health NSLT Lapse</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>-6779.6</v>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HNSLT_USP_RES_S03</t>
+          <t>HNSLT_LAPSE_L_BC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4462,12 +4476,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>G464</t>
+          <t>F132</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>R464C7</t>
+          <t>R132C6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4482,28 +4496,34 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Workers' compensation</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>Health non SLT lapse risk - Liabilities - Initial value</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Article 150 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>Health NSLT Lapse</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>-4067.76</v>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HNSLT_USP_RES_S04</t>
+          <t>HNSLT_LAPSE_L_SH</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4513,12 +4533,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>G465</t>
+          <t>F133</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>R465C7</t>
+          <t>R133C6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4533,28 +4553,36 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Non proportional health reinsurance</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>Health non SLT lapse risk - Liabilities - Value after a mass shock (net)</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Article 150 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HNSLT_USP_NP_FAC_ADJ_S01</t>
+          <t>NL_CAP_SIMPL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4564,22 +4592,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>H462</t>
+          <t>E183</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>R462C8</t>
+          <t>R183C5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4587,11 +4615,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Medical expense</t>
+          <t>Non-life underwriting risk input - Captives simplifications - premium and reserve risk (y/n)</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -4599,13 +4635,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HNSLT_USP_NP_FAC_ADJ_S02</t>
+          <t>NL_ART_116_4_FLG_SEG01</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4615,22 +4655,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>H463</t>
+          <t>E187</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>R463C8</t>
+          <t>R187C5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4638,11 +4678,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Income protection</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Motor vehicle liability insurance and proportional RI</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -4650,13 +4698,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HNSLT_USP_NP_FAC_ADJ_S03</t>
+          <t>NL_ART_116_4_FLG_SEG02</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4666,22 +4718,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>H464</t>
+          <t>E188</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>R464C8</t>
+          <t>R188C5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4689,11 +4741,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Workers' compensation</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Other motor insurance and proportional RI</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -4701,13 +4761,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HNSLT_USP_NP_FAC_ADJ_S04</t>
+          <t>NL_ART_116_4_FLG_SEG03</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4717,22 +4781,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>H465</t>
+          <t>E189</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>R465C8</t>
+          <t>R189C5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4740,11 +4804,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Health - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Non proportional health reinsurance</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Marine, aviation and transport insurance and proportional RI</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -4752,15 +4824,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0.05</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HNSLT_STD_PREM_HRES_SEG01</t>
+          <t>NL_ART_116_4_FLG_SEG04</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4770,22 +4844,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>E474</t>
+          <t>E190</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>R474C5</t>
+          <t>R190C5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4793,11 +4867,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Medical expense and proportional RI</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Fire and other damage to property insurance and proportional RI</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -4805,15 +4887,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.05</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HNSLT_STD_PREM_HRES_SEG02</t>
+          <t>NL_ART_116_4_FLG_SEG05</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4823,22 +4907,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>E475</t>
+          <t>E191</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>R475C5</t>
+          <t>R191C5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4846,11 +4930,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Income protection and proportional RI</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - General liability insurance and proportional RI</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -4858,15 +4950,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0.05</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HNSLT_STD_PREM_HRES_SEG03</t>
+          <t>NL_ART_116_4_FLG_SEG06</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4876,22 +4970,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>E476</t>
+          <t>E192</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>R476C5</t>
+          <t>R192C5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4899,11 +4993,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Premium - Worker's compensation and proportional RI</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Credit and suretyship insurance and proportional RI</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -4911,15 +5013,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0.05</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HNSLT_STD_RES_HRES_SEG01</t>
+          <t>NL_ART_116_4_FLG_SEG07</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4929,22 +5033,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>F474</t>
+          <t>E193</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>R474C6</t>
+          <t>R193C5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4952,11 +5056,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Medical expense and proportional RI</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Legal expenses insurance and proportional RI</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -4964,15 +5076,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>0.05</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HNSLT_STD_RES_HRES_SEG02</t>
+          <t>NL_ART_116_4_FLG_SEG08</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4982,22 +5096,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>F475</t>
+          <t>E194</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>R475C6</t>
+          <t>R194C5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5005,11 +5119,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Income protection and proportional RI</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Assistance and its proportional RI</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -5017,15 +5139,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0.05</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HNSLT_STD_RES_HRES_SEG03</t>
+          <t>NL_ART_116_4_FLG_SEG09</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5035,22 +5159,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>F476</t>
+          <t>E195</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>R476C6</t>
+          <t>R195C5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5058,11 +5182,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>NSLT health underwriting risk input - Premium and reserve risk - HRES - Specific Standard deviations - Reserve - Worker's compensation and proportional RI</t>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Misceallaneous financial loss insurance and proportional RI</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -5070,15 +5202,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Health NSLT Lapse</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>6879.6</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HNSLT_LAPSE_A_BC</t>
+          <t>NL_ART_116_4_FLG_SEG10</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5088,54 +5222,60 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>E132</t>
+          <t>E196</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>R132C5</t>
+          <t>R196C5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Health non SLT lapse risk - Assets - Initial value</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Article 150 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional casualty RI</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Health NSLT Lapse</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>6779.6</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HNSLT_LAPSE_A_SH</t>
+          <t>NL_ART_116_4_FLG_SEG11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5145,54 +5285,60 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>E133</t>
+          <t>E197</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>R133C5</t>
+          <t>R197C5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Health non SLT lapse risk - Assets - Value after a mass shock (net)</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Article 150 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional marine, aviation and transport RI </t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Health NSLT Lapse</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>-6779.6</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HNSLT_LAPSE_L_BC</t>
+          <t>NL_ART_116_4_FLG_SEG12</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5202,54 +5348,60 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>F132</t>
+          <t>E198</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>R132C6</t>
+          <t>R198C5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Health non SLT lapse risk - Liabilities - Initial value</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Article 150 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional property RI</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Health NSLT Lapse</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>-4067.76</v>
+          <t>Non-Life Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2 - USP net</t>
+        </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HNSLT_LAPSE_L_SH</t>
+          <t>NL_USP_STD_DEV_PREM_FLG_S03</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5259,41 +5411,41 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>F133</t>
+          <t>E491</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>R133C6</t>
+          <t>R491C5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>USP Standard deviation gross/net</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Health non SLT lapse risk - Liabilities - Value after a mass shock (net)</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Article 150 [2015/35/EU]</t>
-        </is>
-      </c>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Marine, aviation, transport (MAT)</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5301,14 +5453,12 @@
           <t>Non-Life Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="B90" t="n">
+        <v>0.08</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NL_CAP_SIMPL</t>
+          <t>NL_USP_PREM_S03</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5318,22 +5468,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>E183</t>
+          <t>F491</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>R183C5</t>
+          <t>R491C6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5341,19 +5491,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Captives simplifications - premium and reserve risk (y/n)</t>
+          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Marine, aviation, transport (MAT)</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -5361,17 +5503,15 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>6789.6</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG01</t>
+          <t>NL_LAPSE_A_BC</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5381,60 +5521,54 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>E187</t>
+          <t>E215</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>R187C5</t>
+          <t>R215C5</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Motor vehicle liability insurance and proportional RI</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
+          <t>Non-life lapse risk - Assets - Initial value</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Article 118 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>6779.6</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG02</t>
+          <t>NL_LAPSE_A_SH</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5444,60 +5578,54 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>E188</t>
+          <t>E216</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>R188C5</t>
+          <t>R216C5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Other motor insurance and proportional RI</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
+          <t>Non-life lapse risk - Assets - Value after a mass shock (net)</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Article 118 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>-6779.6</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG03</t>
+          <t>NL_LAPSE_L_BC</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5507,60 +5635,54 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>E189</t>
+          <t>F215</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>R189C5</t>
+          <t>R215C6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Marine, aviation and transport insurance and proportional RI</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
+          <t>Non-life lapse risk - Liabilities - Initial value</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Article 118 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>-4067.76</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG04</t>
+          <t>NL_LAPSE_L_SH</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5570,60 +5692,54 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>E190</t>
+          <t>F216</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>R190C5</t>
+          <t>R216C6</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Fire and other damage to property insurance and proportional RI</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
+          <t>Non-life lapse risk - Liabilities - Value after a mass shock (net)</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Article 118 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>300</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG05</t>
+          <t>NL_WS_OTH_REG_RM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5633,42 +5749,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>E191</t>
+          <t>E250</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>R191C5</t>
+          <t>R250C5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - General liability insurance and proportional RI</t>
+          <t>Non-life catastrophe risk - Windstorm - Other regions - Risk Mitigation</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -5676,17 +5784,15 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>300</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG06</t>
+          <t>NL_WS_OTH_REG_RM_WONB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5696,42 +5802,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>E192</t>
+          <t>F250</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>R192C5</t>
+          <t>R250C6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Credit and suretyship insurance and proportional RI</t>
+          <t>Non-life catastrophe risk - Windstorm - Other regions - Risk Mitigation - Without new business</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -5739,17 +5837,15 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG07</t>
+          <t>NL_WS_OTH_REG_REINS_PREM</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5759,42 +5855,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>E193</t>
+          <t>E251</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>R193C5</t>
+          <t>R251C5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Legal expenses insurance and proportional RI</t>
+          <t>Non-life catastrophe risk - Windstorm - Other regions - Estimated Reinstatement Premiums</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -5802,17 +5890,15 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>300</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG08</t>
+          <t>NL_EQ_OTH_REG_RM</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5822,42 +5908,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>E194</t>
+          <t>E252</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>R194C5</t>
+          <t>R252C5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Assistance and its proportional RI</t>
+          <t>Non-life catastrophe risk - Earthquake - Other regions - Risk Mitigation</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -5865,17 +5943,15 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>300</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG09</t>
+          <t>NL_EQ_OTH_REG_RM_WONB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5885,42 +5961,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>E195</t>
+          <t>F252</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>R195C5</t>
+          <t>R252C6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Misceallaneous financial loss insurance and proportional RI</t>
+          <t>Non-life catastrophe risk - Earthquake - Other regions - Estimated Reinstatement Premiums</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -5928,17 +5996,15 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>100</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG10</t>
+          <t>NL_EQ_OTH_REG_REINS_PREM</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5948,42 +6014,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>E196</t>
+          <t>E253</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>R196C5</t>
+          <t>R253C5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional casualty RI</t>
+          <t>Non-life catastrophe risk - Earthquake - Other regions - Risk Mitigation - Without new business</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -5991,17 +6049,15 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>300</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG11</t>
+          <t>NL_FL_OTH_REG_RM</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6011,42 +6067,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>E197</t>
+          <t>E254</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>R197C5</t>
+          <t>R254C5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional marine, aviation and transport RI </t>
+          <t>Non-life catastrophe risk - Flood - Other regions - Risk Mitigation</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -6054,17 +6102,15 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>300</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NL_ART_116_4_FLG_SEG12</t>
+          <t>NL_FL_OTH_REG_RM_WONB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6074,42 +6120,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>E198</t>
+          <t>F254</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>R198C5</t>
+          <t>R254C6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Non-life underwriting risk input - Premium and reserve risk - Premiums - Article 116 (4) applicable? - Non-proportional property RI</t>
+          <t>Non-life catastrophe risk - Flood - Other regions - Estimated Reinstatement Premiums</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -6117,13 +6155,15 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>100</v>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S01</t>
+          <t>NL_FL_OTH_REG_REINS_PREM</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6133,38 +6173,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>E489</t>
+          <t>E255</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>R489C5</t>
+          <t>R255C5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Motor vehicle liability</t>
+          <t>Non-life catastrophe risk - Flood - Other regions - Risk Mitigation - Without new business</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -6172,13 +6208,15 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>300</v>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S02</t>
+          <t>NL_HA_OTH_REG_RM</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6188,38 +6226,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>E490</t>
+          <t>E256</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>R490C5</t>
+          <t>R256C5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Motor, other classes</t>
+          <t>Non-life catastrophe risk - Hail - Other regions - Risk Mitigation</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -6227,17 +6261,15 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2 - USP net</t>
-        </is>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>300</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S03</t>
+          <t>NL_HA_OTH_REG_RM_WONB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6247,38 +6279,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>E491</t>
+          <t>F256</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>R491C5</t>
+          <t>R256C6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Marine, aviation, transport (MAT)</t>
+          <t>Non-life catastrophe risk - Hail - Other regions - Estimated Reinstatement Premiums</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -6286,13 +6314,15 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>100</v>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S04</t>
+          <t>NL_HA_OTH_REG_REINS_PREM</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6302,38 +6332,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>E492</t>
+          <t>E257</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>R492C5</t>
+          <t>R257C5</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Fire and other property damage</t>
+          <t>Non-life catastrophe risk - Hail - Other regions - Risk Mitigation - Without new business</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -6341,13 +6367,15 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2000</v>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S05</t>
+          <t>NL_NPPRI_PREM_EARN_G_NY_EB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6357,38 +6385,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>E493</t>
+          <t>E272</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>R493C5</t>
+          <t>R272C5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Third-party liability</t>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Gross premium to be earned - Existing business</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -6396,13 +6420,15 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S06</t>
+          <t>NL_NPPRI_PREM_EARN_G_NY_NB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6412,38 +6438,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>E494</t>
+          <t>F272</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>R494C5</t>
+          <t>R272C6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Credit and suretyship</t>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Gross premium to be earned - New business</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -6451,13 +6473,15 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>300</v>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S07</t>
+          <t>NL_NPPRI_RM</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6467,38 +6491,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>E495</t>
+          <t>E278</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>R495C5</t>
+          <t>R278C5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Legal expenses</t>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Risk Mitigation</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -6506,13 +6526,15 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>300</v>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S08</t>
+          <t>NL_NPPRI_RM_WONB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6522,38 +6544,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>E496</t>
+          <t>F278</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>R496C5</t>
+          <t>R278C6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Assistance</t>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Risk Mitigation - Without new business</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -6561,13 +6579,15 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>100</v>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S09</t>
+          <t>NL_NPPRI_REINS_PREM</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6577,38 +6597,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>E497</t>
+          <t>E279</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>R497C5</t>
+          <t>R279C5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Miscellaneous</t>
+          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Estimated Reinstatement Premiums</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -6616,13 +6632,15 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S10</t>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6632,38 +6650,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>E498</t>
+          <t>E297</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>R498C5</t>
+          <t>R297C5</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Non-proportional reinsurance - casualty</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -6671,13 +6685,15 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S11</t>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6687,38 +6703,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>E499</t>
+          <t>E298</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>R499C5</t>
+          <t>R298C5</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Non-proportional reinsurance - MAT</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -6726,13 +6738,15 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NL_USP_STD_DEV_PREM_FLG_S12</t>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6742,38 +6756,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>E500</t>
+          <t>E299</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>R500C5</t>
+          <t>R299C5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>USP Standard deviation gross/net</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Standard deviation gross/net?   Segment: Non-proportional reinsurance - property</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -6781,13 +6791,15 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S01</t>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP4</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6797,12 +6809,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>F489</t>
+          <t>E300</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>R489C6</t>
+          <t>R300C5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6817,14 +6829,14 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Motor vehicle liability</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional casualty RI other than General Liability RI</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -6832,13 +6844,15 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S02</t>
+          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP5</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6848,12 +6862,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>F490</t>
+          <t>E301</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>R490C6</t>
+          <t>R301C5</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6868,14 +6882,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Motor, other classes</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional Credit &amp; Suretyship RI</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -6883,15 +6897,15 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
+          <t>Non-Life Cat.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S03</t>
+          <t>NL_OTHCAT_RM_GROUP1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6901,12 +6915,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>F491</t>
+          <t>G297</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>R491C6</t>
+          <t>R297C7</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6921,14 +6935,14 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Marine, aviation, transport (MAT)</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -6936,13 +6950,15 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S04</t>
+          <t>NL_OTHCAT_RM_GROUP2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6952,12 +6968,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>F492</t>
+          <t>G298</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>R492C6</t>
+          <t>R298C7</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6972,14 +6988,14 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Fire and other property damage</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -6987,13 +7003,15 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S05</t>
+          <t>NL_OTHCAT_RM_GROUP3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7003,12 +7021,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>F493</t>
+          <t>G299</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>R493C6</t>
+          <t>R299C7</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7023,14 +7041,14 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Third-party liability</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -7038,13 +7056,15 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S06</t>
+          <t>NL_OTHCAT_RM_GROUP4</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7054,12 +7074,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>F494</t>
+          <t>G300</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>R494C6</t>
+          <t>R300C7</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7074,14 +7094,14 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Credit and suretyship</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional casualty RI other than General Liability RI</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -7089,13 +7109,15 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S07</t>
+          <t>NL_OTHCAT_RM_GROUP5</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7105,12 +7127,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>F495</t>
+          <t>G301</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>R495C6</t>
+          <t>R301C7</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7125,14 +7147,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Legal expenses</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional Credit &amp; Suretyship RI</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -7140,13 +7162,15 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S08</t>
+          <t>NL_OTHCAT_RM_WONB_GROUP1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7156,12 +7180,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>F496</t>
+          <t>H297</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>R496C6</t>
+          <t>R297C8</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7176,14 +7200,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Assistance</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -7191,13 +7215,15 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S09</t>
+          <t>NL_OTHCAT_RM_WONB_GROUP2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7207,12 +7233,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>F497</t>
+          <t>H298</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>R497C6</t>
+          <t>R298C8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7227,14 +7253,14 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Miscellaneous</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -7242,13 +7268,15 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S10</t>
+          <t>NL_OTHCAT_RM_WONB_GROUP3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7258,12 +7286,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>F498</t>
+          <t>H299</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>R498C6</t>
+          <t>R299C8</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7278,14 +7306,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Non-proportional reinsurance - casualty</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -7293,13 +7321,15 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S11</t>
+          <t>NL_OTHCAT_RM_WONB_GROUP4</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7309,12 +7339,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>F499</t>
+          <t>H300</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>R499C6</t>
+          <t>R300C8</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7329,14 +7359,14 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Non-proportional reinsurance - MAT</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional casualty RI other than General Liability RI</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -7344,13 +7374,15 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>Non-Life Cat.</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NL_USP_PREM_S12</t>
+          <t>NL_OTHCAT_RM_WONB_GROUP5</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7360,12 +7392,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>F500</t>
+          <t>H301</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>R500C6</t>
+          <t>R301C8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7380,14 +7412,14 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Premium risk Segment: Non-proportional reinsurance - property</t>
+          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional Credit &amp; Suretyship RI</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -7395,13 +7427,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>Risk Margin</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Method 3</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S01</t>
+          <t>RM_METHOD</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7411,17 +7447,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>G489</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>R489C7</t>
+          <t>R37C5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7434,11 +7470,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Risk Margin Method</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Motor vehicle liability</t>
+          <t>Risk margin - Method chosen for risk margin calculations</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -7446,13 +7486,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>Risk Margin</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S02</t>
+          <t>RM_ART_116_147_4_FLG</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7462,22 +7506,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>G490</t>
+          <t>E39</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>R490C7</t>
+          <t>R39C5</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7485,11 +7529,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Motor, other classes</t>
+          <t>Risk margin - Article 116 (4) and Article 147 (4) applicable?</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -7497,13 +7549,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>Risk Margin - Method 2</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>net SCR</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S03</t>
+          <t>RM_PROJECTION</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7513,17 +7569,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>G491</t>
+          <t>E38</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>R491C7</t>
+          <t>R38C5</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7536,11 +7592,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Projection method 2</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>gross SCR</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Marine, aviation, transport (MAT)</t>
+          <t>Risk margin - Method 2 - Projection of gross or net SCR</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -7548,13 +7612,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>Risk Margin - Split</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S04</t>
+          <t>RM_TC_SPLIT_FLG</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7564,22 +7632,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>G492</t>
+          <t>E43</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>R492C7</t>
+          <t>R43C5</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7587,11 +7655,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Fire and other property damage</t>
+          <t>Risk margin - Allocation - Split of Risk Margin by currency necessary?</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -7599,13 +7675,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>Risk Margin - Split</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S05</t>
+          <t>RM_TC_SPLIT_ALLOC_FLG</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7615,22 +7695,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>G493</t>
+          <t>E44</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>R493C7</t>
+          <t>R44C5</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7638,11 +7718,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Flag yes/no</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Third-party liability</t>
+          <t>Risk margin - Split by currency - Flag for allocation factors</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -7650,13 +7738,15 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.08</v>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S06</t>
+          <t>LIFE_REV_SHOCK_USP</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7666,12 +7756,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>G494</t>
+          <t>E439</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>R494C7</t>
+          <t>R439C5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7693,7 +7783,7 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Credit and suretyship</t>
+          <t xml:space="preserve">Life underwriting risk - Revision Risk - Revision shock used - USP </t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -7701,13 +7791,15 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>Health SLT</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.04</v>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S07</t>
+          <t>HSLT_REV_SHOCK_USP</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7717,12 +7809,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>G495</t>
+          <t>E447</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>R495C7</t>
+          <t>R447C5</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7744,7 +7836,7 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Legal expenses</t>
+          <t xml:space="preserve">SLT health underwriting risk - Revision Risk - Revision shock used - USP </t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -7752,13 +7844,15 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>548</v>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S08</t>
+          <t>NSCR_REMAINING_PART</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7768,12 +7862,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>G496</t>
+          <t>F545</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>R496C7</t>
+          <t>R545C6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -7788,28 +7882,34 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Assistance</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr"/>
+          <t>Total amount of Notional Solvency Capital Requirements for remaining part</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>450</v>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S09</t>
+          <t>NSCR_RFF</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7819,12 +7919,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>G497</t>
+          <t>F546</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>R497C7</t>
+          <t>R546C6</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -7839,28 +7939,34 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Miscellaneous</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr"/>
+          <t>Total amount of Notional Solvency Capital Requirements for ring fenced funds</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>666</v>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S10</t>
+          <t>NSCR_MAP</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7870,12 +7976,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>G498</t>
+          <t>F547</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>R498C7</t>
+          <t>R547C6</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -7890,28 +7996,34 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Non-proportional reinsurance - casualty</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr"/>
+          <t>Total amount of Notional Solvency Capital Requirement for matching adjustment portfolios</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>-981</v>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S11</t>
+          <t>DIV_EFFECT_RFF_304</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7921,12 +8033,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>G499</t>
+          <t>F548</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>R499C7</t>
+          <t>R548C6</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -7941,28 +8053,36 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Non-proportional reinsurance - MAT</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr"/>
+          <t>Diversification effects due to RFF nSCR aggregation for article 304</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Article 216 (2.) [2015/35/EU]; Article 304 [2009/138/EC]</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+          <t>RFF/MAP</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>4 = No adjustment (Default Value)</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>NL_USP_RES_S12</t>
+          <t>ADJ_RFF_MAP_METH</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7972,22 +8092,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>G500</t>
+          <t>F549</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>R500C7</t>
+          <t>R549C6</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -7995,25 +8115,41 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>List RFF/MAP Method</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>4 = No adjustment (Default Value)</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - Reserve risk Segment: Non-proportional reinsurance - property</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr"/>
+          <t xml:space="preserve">Method used to calculate the adjustment due to RFF/MAP nSCR aggregation </t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Cell on S.25.01.01 QRT</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>Health NSLT Prem. &amp; Res.</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NL_USP_NP_FAC_ADJ_S01</t>
+          <t>HNSLT_LAPSE_SIMPL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8023,22 +8159,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>H489</t>
+          <t>E140</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>R489C8</t>
+          <t>R140C5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8046,11 +8182,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Simplification NSLT</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Motor vehicle liability</t>
+          <t>Simplification Health</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -8058,13 +8202,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>Non-Life Lapse</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NL_USP_NP_FAC_ADJ_S02</t>
+          <t>NL_LAPSE_SIMPL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8074,22 +8222,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>H490</t>
+          <t>E221</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>R490C8</t>
+          <t>R221C5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8097,11 +8245,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Simplification NSLT NL</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Motor, other classes</t>
+          <t>Simplification Non Life</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -8112,10 +8268,14 @@
           <t>Non-Life Prem. &amp; Res.</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NL_USP_NP_FAC_ADJ_S03</t>
+          <t>NL_WS_SIMPL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8125,22 +8285,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>H491</t>
+          <t>E237</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>R491C8</t>
+          <t>R237C5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8148,25 +8308,33 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Marine, aviation, transport (MAT)</t>
-        </is>
-      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Simplification NC</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>9 - no simplification</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>Participant information</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Standard Formula</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NL_USP_NP_FAC_ADJ_S04</t>
+          <t>INFO_TYPE_OF_MODEL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8176,22 +8344,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>H492</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>R492C8</t>
+          <t>R18C5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8199,3867 +8367,22 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Type of Model</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Standard Formula</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Fire and other property damage</t>
+          <t>Internal Model</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>NL_USP_NP_FAC_ADJ_S05</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>H493</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>R493C8</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Third-party liability</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>NL_USP_NP_FAC_ADJ_S06</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>H494</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>R494C8</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Credit and suretyship</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>NL_USP_NP_FAC_ADJ_S07</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>H495</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>R495C8</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Legal expenses</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>NL_USP_NP_FAC_ADJ_S08</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>H496</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>R496C8</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Assistance</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>NL_USP_NP_FAC_ADJ_S09</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>H497</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>R497C8</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Miscellaneous</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>NL_USP_NP_FAC_ADJ_S10</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>H498</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>R498C8</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Non-proportional reinsurance - casualty</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>NL_USP_NP_FAC_ADJ_S11</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>H499</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>R499C8</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Non-proportional reinsurance - MAT</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>NL_USP_NP_FAC_ADJ_S12</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>H500</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>R500C8</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>Non-Life - Prem. &amp; Res. Risk - USP - NP factor for adjustment Segment: Non-proportional reinsurance - property</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>6789.6</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>NL_LAPSE_A_BC</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>E215</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>R215C5</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>Non-life lapse risk - Assets - Initial value</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>Article 118 [2015/35/EU]</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>6779.6</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>NL_LAPSE_A_SH</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>E216</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>R216C5</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>Non-life lapse risk - Assets - Value after a mass shock (net)</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>Article 118 [2015/35/EU]</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>-6779.6</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>NL_LAPSE_L_BC</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>F215</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>R215C6</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>Non-life lapse risk - Liabilities - Initial value</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>Article 118 [2015/35/EU]</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>-4067.76</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>NL_LAPSE_L_SH</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>F216</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>R216C6</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>Non-life lapse risk - Liabilities - Value after a mass shock (net)</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>Article 118 [2015/35/EU]</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>300</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>NL_WS_OTH_REG_RM</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>E250</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>R250C5</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Windstorm - Other regions - Risk Mitigation</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>300</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>NL_WS_OTH_REG_RM_WONB</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>F250</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>R250C6</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Windstorm - Other regions - Risk Mitigation - Without new business</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>100</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>NL_WS_OTH_REG_REINS_PREM</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>E251</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>R251C5</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Windstorm - Other regions - Estimated Reinstatement Premiums</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>NL_WS_OTH_REG_REINS_PREM_WONB</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>F251</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>R251C6</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Windstorm - Other regions - Estimated Reinstatement Premiums - Without new business</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>300</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>NL_EQ_OTH_REG_RM</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>E252</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>R252C5</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Earthquake - Other regions - Risk Mitigation</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>300</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>NL_EQ_OTH_REG_RM_WONB</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>F252</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>R252C6</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Earthquake - Other regions - Estimated Reinstatement Premiums</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>100</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>NL_EQ_OTH_REG_REINS_PREM</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>E253</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>R253C5</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Earthquake - Other regions - Risk Mitigation - Without new business</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>NL_EQ_OTH_REG_REINS_PREM_WONB</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>F253</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>R253C6</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Earthquake - Other regions - Estimated Reinstatement Premiums - Without new business</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>300</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>NL_FL_OTH_REG_RM</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>E254</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>R254C5</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Flood - Other regions - Risk Mitigation</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>300</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>NL_FL_OTH_REG_RM_WONB</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>F254</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>R254C6</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Flood - Other regions - Estimated Reinstatement Premiums</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>100</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>NL_FL_OTH_REG_REINS_PREM</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>E255</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>R255C5</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Flood - Other regions - Risk Mitigation - Without new business</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>NL_FL_OTH_REG_REINS_PREM_WONB</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>F255</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>R255C6</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Flood - Other regions - Estimated Reinstatement Premiums - Without new business</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>300</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>NL_HA_OTH_REG_RM</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>E256</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>R256C5</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Hail - Other regions - Risk Mitigation</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>300</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>NL_HA_OTH_REG_RM_WONB</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>F256</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>R256C6</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Hail - Other regions - Estimated Reinstatement Premiums</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>100</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>NL_HA_OTH_REG_REINS_PREM</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>E257</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>R257C5</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Hail - Other regions - Risk Mitigation - Without new business</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr"/>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>NL_HA_OTH_REG_REINS_PREM_WONB</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>F257</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>R257C6</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Hail - Other regions - Estimated Reinstatement Premiums - Without new business</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>NL_NPPRI_PREM_EARN_G_NY_EB</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>E272</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>R272C5</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Gross premium to be earned - Existing business</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>NL_NPPRI_PREM_EARN_G_NY_NB</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>F272</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>R272C6</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Gross premium to be earned - New business</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>300</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>NL_NPPRI_RM</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>E278</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>R278C5</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Risk Mitigation</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>300</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>NL_NPPRI_RM_WONB</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>F278</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>R278C6</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Risk Mitigation - Without new business</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>100</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>NL_NPPRI_REINS_PREM</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>E279</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>R279C5</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Non-proportional property reinsurance - Estimated Reinstatement Premiums</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>0</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP1</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>E297</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>R297C5</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP2</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>E298</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>R298C5</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>0</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP3</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>E299</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>R299C5</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
-        </is>
-      </c>
-      <c r="M178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP4</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>E300</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>R300C5</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional casualty RI other than General Liability RI</t>
-        </is>
-      </c>
-      <c r="M179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>0</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_EB_GROUP5</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>E301</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>R301C5</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - existing business - Non-proportional Credit &amp; Suretyship RI</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP1</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>F297</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>R297C6</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP2</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>F298</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>R298C6</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP3</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>F299</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>R299C6</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
-        </is>
-      </c>
-      <c r="M183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP4</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>F300</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>R300C6</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Non-proportional casualty RI other than General Liability RI</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_PR_EA_G_NY_NB_GROUP5</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>F301</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>R301C6</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - gross premium expected to be earned in following 12 months - new business - Non-proportional Credit &amp; Suretyship RI</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>0</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_GROUP1</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>G297</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>R297C7</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>0</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_GROUP2</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>G298</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>R298C7</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>0</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_GROUP3</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>G299</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>R299C7</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
-        </is>
-      </c>
-      <c r="M188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>0</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_GROUP4</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>G300</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>R300C7</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional casualty RI other than General Liability RI</t>
-        </is>
-      </c>
-      <c r="M189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>0</v>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_GROUP5</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>G301</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>R301C7</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - Non-proportional Credit &amp; Suretyship RI</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>0</v>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP1</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>H297</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>R297C8</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Marine, aviation and transport insurance and proportional RI other than Marine or Aviation insurancen and RI</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>0</v>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP2</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>H298</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>R298C8</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional marine, aviation and transport RI other than Marine RI and Aviation RI</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>0</v>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP3</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>H299</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>R299C8</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Misceallaneous financial loss insurance and proportional RI other than extended warranty</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP4</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>H300</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>R300C8</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional casualty RI other than General Liability RI</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Non-Life Cat.</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>0</v>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>NL_OTHCAT_RM_WONB_GROUP5</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>H301</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>R301C8</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>Non-life catastrophe risk - Other non-life cat risk - Mitigation - without new business - Non-proportional Credit &amp; Suretyship RI</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Risk Margin</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Method 3</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>RM_METHOD</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>E37</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>R37C5</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>Risk Margin Method</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>Risk margin - Method chosen for risk margin calculations</t>
-        </is>
-      </c>
-      <c r="M196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Risk Margin</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>RM_ART_116_147_4_FLG</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>E39</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>R39C5</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>Risk margin - Article 116 (4) and Article 147 (4) applicable?</t>
-        </is>
-      </c>
-      <c r="M197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Risk Margin - Method 2</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>net SCR</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>RM_PROJECTION</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>E38</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>R38C5</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>Projection method 2</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>gross SCR</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>Risk margin - Method 2 - Projection of gross or net SCR</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Risk Margin - Split</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>RM_TC_SPLIT_FLG</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>E43</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>R43C5</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>Risk margin - Allocation - Split of Risk Margin by currency necessary?</t>
-        </is>
-      </c>
-      <c r="M199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Risk Margin - Split</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>RM_TC_SPLIT_ALLOC_FLG</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>E44</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>R44C5</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>Flag yes/no</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>Risk margin - Split by currency - Flag for allocation factors</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>LIFE_REV_SHOCK_USP</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>E439</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>R439C5</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Life underwriting risk - Revision Risk - Revision shock used - USP </t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Health SLT</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>HSLT_REV_SHOCK_USP</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>E447</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>R447C5</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SLT health underwriting risk - Revision Risk - Revision shock used - USP </t>
-        </is>
-      </c>
-      <c r="M202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>548</v>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>NSCR_REMAINING_PART</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>F545</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>R545C6</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>Total amount of Notional Solvency Capital Requirements for remaining part</t>
-        </is>
-      </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>450</v>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>NSCR_RFF</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>F546</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>R546C6</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>Total amount of Notional Solvency Capital Requirements for ring fenced funds</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>666</v>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>NSCR_MAP</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>F547</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>R547C6</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>Total amount of Notional Solvency Capital Requirement for matching adjustment portfolios</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>Article 216 (1.) &amp; 217 [2015/35/EU]</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>-981</v>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>DIV_EFFECT_RFF_304</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>F548</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>R548C6</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>Diversification effects due to RFF nSCR aggregation for article 304</t>
-        </is>
-      </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>Article 216 (2.) [2015/35/EU]; Article 304 [2009/138/EC]</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>RFF/MAP</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>4 = No adjustment (Default Value)</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>ADJ_RFF_MAP_METH</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>F549</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>R549C6</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>List RFF/MAP Method</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>4 = No adjustment (Default Value)</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Method used to calculate the adjustment due to RFF/MAP nSCR aggregation </t>
-        </is>
-      </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>Cell on S.25.01.01 QRT</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Health NSLT Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>HNSLT_LAPSE_SIMPL</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>E140</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>R140C5</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>Simplification NSLT</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>Simplification Health</t>
-        </is>
-      </c>
-      <c r="M208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Non-Life Lapse</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>NL_LAPSE_SIMPL</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>E221</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>R221C5</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>Simplification NSLT NL</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>Simplification Non Life</t>
-        </is>
-      </c>
-      <c r="M209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Non-Life Prem. &amp; Res.</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>NL_WS_SIMPL</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>E237</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>R237C5</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>Simplification NC</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>9 - no simplification</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>SCR</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr"/>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>SCR_PRELIMINARY_VTP</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>E47</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>R47C5</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>Preliminary SCR</t>
-        </is>
-      </c>
-      <c r="M211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>SCR</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>SCR_PRELIMINARY_TTP</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>E48</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>R48C5</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>Preliminary SCR</t>
-        </is>
-      </c>
-      <c r="M212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Participant information</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Standard Formula</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>INFO_TYPE_OF_MODEL</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Basic input</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>R18C5</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>Type of Model</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>Standard Formula</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>Internal Model</t>
-        </is>
-      </c>
-      <c r="M213" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
